--- a/ci-cd-merge-resolver/repoCollector/datasets/WxJava.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/WxJava.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -44,13 +44,22 @@
     <t>isMultiModule</t>
   </si>
   <si>
-    <t>516c1cc80a23e8188c9b231f3f4ea55c40e9e947</t>
-  </si>
-  <si>
-    <t>1ab807d752b3e315d914b141c06da1bb3d5b2b98</t>
-  </si>
-  <si>
-    <t>e84325d0e4010015da62e7661b9720fa12e5d833</t>
+    <t>7a816cf7a9d190902b7df000d3ab9a23b1d03280</t>
+  </si>
+  <si>
+    <t>e492e5adebca7603609ca97799fc478959fa03fe</t>
+  </si>
+  <si>
+    <t>d08174991e08bb7aee882569b82c91c97fe9ecab</t>
+  </si>
+  <si>
+    <t>defd54b2b14bebcfa51807582b3b329b17fdb1a1</t>
+  </si>
+  <si>
+    <t>b403551a8ee097e5720797b39f96f85f9fe0812d</t>
+  </si>
+  <si>
+    <t>39c2f090085e1054de1d12bd0c35dc16764036c1</t>
   </si>
 </sst>
 </file>
@@ -95,7 +104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -141,13 +150,13 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G2" t="b" s="0">
         <v>0</v>
@@ -156,10 +165,42 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>0.7089999914169312</v>
+        <v>7.993000030517578</v>
       </c>
       <c r="J2" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="E3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G3" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H3" t="b" s="0">
         <v>1</v>
+      </c>
+      <c r="I3" t="n" s="0">
+        <v>7.840000152587891</v>
+      </c>
+      <c r="J3" t="b" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
